--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2057,6 +2057,311 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127450501</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96696</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Galgbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>560002</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6700087</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127450552</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Galgbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>559999</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6700076</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127450510</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Galgbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>560014</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6700048</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 54380-2020 artfynd.xlsx
+++ b/artfynd/A 54380-2020 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>127450501</v>
       </c>
       <c r="B14" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>127450552</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>127450510</v>
       </c>
       <c r="B16" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
